--- a/project/HW7/22127435/22127435_APITesting_100/22127435_TestSummaryReport.xlsx
+++ b/project/HW7/22127435/22127435_APITesting_100/22127435_TestSummaryReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/htthanh/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viett\OneDrive\Documents\GitHub\Testing-PRJ-SM\project\HW7\22127435\22127435_APITesting_100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED215DA-9A80-9949-8C9C-635701E02DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B670AB0-5BB8-4FE2-A700-393F6B12BCEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26120" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary Report" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>TEST REPORT</t>
   </si>
@@ -117,16 +117,22 @@
     <t>DEFECT SEVERITY DISTRIBUTION</t>
   </si>
   <si>
-    <t>&lt;Project name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Group id&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Creator&gt;</t>
-  </si>
-  <si>
     <t>&lt;Approver&gt;</t>
+  </si>
+  <si>
+    <t>The Tool Shop</t>
+  </si>
+  <si>
+    <t>Vo Le Viet Tu</t>
+  </si>
+  <si>
+    <t>UC01</t>
+  </si>
+  <si>
+    <t>UC03</t>
+  </si>
+  <si>
+    <t>UC02</t>
   </si>
 </sst>
 </file>
@@ -177,6 +183,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,6 +191,7 @@
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -191,6 +199,7 @@
       <sz val="20"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -198,18 +207,21 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -746,17 +758,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
-    <col min="3" max="7" width="10.83203125" style="2"/>
-    <col min="8" max="8" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="5.69921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.796875" customWidth="1"/>
+    <col min="3" max="7" width="10.796875" style="2"/>
+    <col min="8" max="8" width="13.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.796875" style="2"/>
     <col min="10" max="10" width="13" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
@@ -768,13 +780,13 @@
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
@@ -788,13 +800,13 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="23"/>
-      <c r="C3" s="22" t="s">
-        <v>27</v>
+      <c r="C3" s="22">
+        <v>7</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
@@ -803,12 +815,12 @@
       </c>
       <c r="G3" s="23"/>
       <c r="H3" s="22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="22"/>
     </row>
-    <row r="4" spans="1:10" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>18</v>
       </c>
@@ -822,13 +834,13 @@
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="12">
         <f>C16/I16</f>
-        <v>0.46226415094339623</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>14</v>
@@ -837,16 +849,16 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="12">
         <f>D16/I16</f>
-        <v>0.330188679245283</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>1</v>
       </c>
@@ -878,100 +890,94 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5">
         <f>SUM(D10:F10)</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E10" s="5">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5">
-        <v>3</v>
-      </c>
-      <c r="G10" s="5">
-        <v>7</v>
-      </c>
-      <c r="H10" s="5">
-        <v>18</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="5">
         <f>SUM(C10,G10:H10)</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J10" s="6">
         <f>C10/I10</f>
-        <v>0.47916666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5">
         <f>SUM(D11:F11)</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="5">
-        <v>4</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2</v>
-      </c>
-      <c r="G11" s="5">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5">
-        <v>22</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="5">
         <f>SUM(C11,G11:H11)</f>
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="J11" s="6">
         <f>C11/I11</f>
-        <v>0.44827586206896552</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>3</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="C12" s="5">
         <f t="shared" ref="C12:C14" si="0">SUM(D12:F12)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="D12" s="5">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5">
+        <v>6</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5">
         <f t="shared" ref="I12:I14" si="1">SUM(C12,G12:H12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="e">
+        <v>32</v>
+      </c>
+      <c r="J12" s="6">
         <f t="shared" ref="J12:J14" si="2">C12/I12</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>4</v>
       </c>
@@ -994,7 +1000,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>5</v>
       </c>
@@ -1017,7 +1023,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -1029,51 +1035,51 @@
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="13">
         <f t="shared" ref="C16:I16" si="3">SUM(C10:C14)</f>
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D16" s="8">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F16" s="8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I16" s="13">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="J16" s="12">
         <f>C16/I16</f>
-        <v>0.46226415094339623</v>
-      </c>
-    </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J19" s="3"/>
     </row>
   </sheetData>
@@ -1103,13 +1109,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.1640625" customWidth="1"/>
+    <col min="2" max="2" width="27.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="21" t="s">
         <v>25</v>
       </c>
@@ -1118,7 +1124,7 @@
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -1141,7 +1147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1191,7 +1197,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -1208,7 +1214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -1251,7 +1257,7 @@
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
         <v>10</v>
